--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\Alandon Tow Service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D478C7F6-F13B-4D7E-8C57-E4857E33251A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA13AC79-9FB6-4A4A-A791-F3C284D5B509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1665" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5394" uniqueCount="1710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5805" uniqueCount="1824">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -193,15 +193,15 @@
     <t>01/06/26 19:00 EST</t>
   </si>
   <si>
+    <t>3.3mi E of Kansas City KS</t>
+  </si>
+  <si>
     <t>Dustin Porter</t>
   </si>
   <si>
     <t>4.2mi S of Tonganoxie KS</t>
   </si>
   <si>
-    <t>3.3mi E of Kansas City KS</t>
-  </si>
-  <si>
     <t>28.2mi W of Maryville MO</t>
   </si>
   <si>
@@ -4897,9 +4897,6 @@
     <t>03/10/26 20:57 EDT</t>
   </si>
   <si>
-    <t>03/10/26 21:22 EDT</t>
-  </si>
-  <si>
     <t>03/10/26 21:44 EDT</t>
   </si>
   <si>
@@ -4921,39 +4918,6 @@
     <t>03/12/26 10:17 EDT</t>
   </si>
   <si>
-    <t>03/11/26 12:18 EDT</t>
-  </si>
-  <si>
-    <t>4.6mi NW of Independence MO</t>
-  </si>
-  <si>
-    <t>03/11/26 12:58 EDT</t>
-  </si>
-  <si>
-    <t>2.3mi N of Raytown MO</t>
-  </si>
-  <si>
-    <t>03/11/26 16:20 EDT</t>
-  </si>
-  <si>
-    <t>03/11/26 18:02 EDT</t>
-  </si>
-  <si>
-    <t>1.6mi S of Kansas City KS</t>
-  </si>
-  <si>
-    <t>03/11/26 18:03 EDT</t>
-  </si>
-  <si>
-    <t>1.4mi N of Shawnee KS</t>
-  </si>
-  <si>
-    <t>03/11/26 18:17 EDT</t>
-  </si>
-  <si>
-    <t>3mi E of Kansas City KS</t>
-  </si>
-  <si>
     <t>03/11/26 18:23 EDT</t>
   </si>
   <si>
@@ -4969,12 +4933,6 @@
     <t>2.8mi W of Lenexa KS</t>
   </si>
   <si>
-    <t>03/11/26 20:15 EDT</t>
-  </si>
-  <si>
-    <t>16.1mi S of Nevada MO</t>
-  </si>
-  <si>
     <t>03/11/26 21:17 EDT</t>
   </si>
   <si>
@@ -4990,42 +4948,15 @@
     <t>03/12/26 03:06 EDT</t>
   </si>
   <si>
-    <t>03/12/26 03:23 EDT</t>
-  </si>
-  <si>
-    <t>03/12/26 03:24 EDT</t>
-  </si>
-  <si>
     <t>03/12/26 06:45 EDT</t>
   </si>
   <si>
     <t>03/12/26 08:27 EDT</t>
   </si>
   <si>
-    <t>03/12/26 10:21 EDT</t>
-  </si>
-  <si>
-    <t>3.5mi E of Lawrence KS</t>
-  </si>
-  <si>
-    <t>03/12/26 13:57 EDT</t>
-  </si>
-  <si>
-    <t>03/12/26 14:41 EDT</t>
-  </si>
-  <si>
-    <t>1.5mi SE of Shawnee KS</t>
-  </si>
-  <si>
     <t>03/12/26 15:06 EDT</t>
   </si>
   <si>
-    <t>03/12/26 15:39 EDT</t>
-  </si>
-  <si>
-    <t>3.1mi S of Kansas City KS</t>
-  </si>
-  <si>
     <t>03/12/26 16:45 EDT</t>
   </si>
   <si>
@@ -5041,12 +4972,6 @@
     <t>03/13/26 10:17 EDT</t>
   </si>
   <si>
-    <t>03/12/26 20:22 EDT</t>
-  </si>
-  <si>
-    <t>2.9mi SE of Gladstone MO</t>
-  </si>
-  <si>
     <t>03/12/26 20:26 EDT</t>
   </si>
   <si>
@@ -5059,97 +4984,514 @@
     <t>12.1mi N of Kearney MO</t>
   </si>
   <si>
+    <t>03/16/26 11:58 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 12:07 EDT</t>
+  </si>
+  <si>
     <t>03/12/26 21:37 EDT</t>
   </si>
   <si>
+    <t>03/16/26 11:59 EDT</t>
+  </si>
+  <si>
     <t>03/12/26 22:09 EDT</t>
   </si>
   <si>
     <t>03/13/26 09:41 EDT</t>
   </si>
   <si>
-    <t>03/13/26 10:22 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 10:24 EDT</t>
-  </si>
-  <si>
-    <t>0.4mi SW of Basehor KS</t>
-  </si>
-  <si>
-    <t>4.6mi SE of Lansing KS</t>
-  </si>
-  <si>
-    <t>03/13/26 10:25 EDT</t>
-  </si>
-  <si>
-    <t>0.5mi SW of Basehor KS</t>
-  </si>
-  <si>
-    <t>03/13/26 11:05 EDT</t>
-  </si>
-  <si>
-    <t>2.9mi S of Overland Park KS</t>
-  </si>
-  <si>
-    <t>03/13/26 11:17 EDT</t>
+    <t>03/13/26 13:08 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 17:35 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 19:01 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi NW of Raytown MO</t>
+  </si>
+  <si>
+    <t>03/13/26 20:15 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 12:01 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 20:39 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 20:51 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi SE of Lenexa KS</t>
+  </si>
+  <si>
+    <t>03/13/26 21:19 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi S of Olathe KS</t>
+  </si>
+  <si>
+    <t>03/13/26 22:04 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 02:18 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 08:39 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 18:19 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 18:52 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi S of Bonner Springs KS</t>
+  </si>
+  <si>
+    <t>03/14/26 19:35 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 20:00 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 23:42 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi N of Bonner Springs KS</t>
+  </si>
+  <si>
+    <t>03/16/26 12:04 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 12:35 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 15:36 EDT</t>
+  </si>
+  <si>
+    <t>0.2mi NW of Tonganoxie KS</t>
+  </si>
+  <si>
+    <t>03/16/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 20:09 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 21:14 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 02:24 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 04:19 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 05:34 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 10:46 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi NW of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/16/26 13:19 EDT</t>
+  </si>
+  <si>
+    <t>21.9mi NW of Savannah MO</t>
+  </si>
+  <si>
+    <t>03/17/26 09:17 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 21:09 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi W of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/16/26 21:14 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 22:29 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi E of Gardner KS</t>
+  </si>
+  <si>
+    <t>03/16/26 22:39 EDT</t>
+  </si>
+  <si>
+    <t>17mi S of Harrisonville MO</t>
+  </si>
+  <si>
+    <t>03/16/26 23:24 EDT</t>
+  </si>
+  <si>
+    <t>27mi S of Harrisonville MO</t>
+  </si>
+  <si>
+    <t>03/16/26 23:39 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi N of Tonganoxie KS</t>
+  </si>
+  <si>
+    <t>03/16/26 23:44 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:49 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 20:10 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 21:04 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 05:02 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 05:47 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 07:33 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 07:58 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 10:41 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:37 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi W of Prairie Village KS</t>
+  </si>
+  <si>
+    <t>03/19/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>9.9mi S of St. Joseph MO</t>
+  </si>
+  <si>
+    <t>03/18/26 11:46 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:52 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi E of Kansas City KS</t>
+  </si>
+  <si>
+    <t>03/18/26 11:53 EDT</t>
+  </si>
+  <si>
+    <t>5mi E of Kansas City KS</t>
+  </si>
+  <si>
+    <t>03/18/26 11:55 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:57 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi SE of Parkville MO</t>
+  </si>
+  <si>
+    <t>03/18/26 11:58 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 12:02 EDT</t>
+  </si>
+  <si>
+    <t>4.2mi SW of Savannah MO</t>
+  </si>
+  <si>
+    <t>03/18/26 12:15 EDT</t>
+  </si>
+  <si>
+    <t>11.4mi W of Savannah MO</t>
+  </si>
+  <si>
+    <t>03/18/26 12:26 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 13:45 EDT</t>
+  </si>
+  <si>
+    <t>8.8mi W of Savannah MO</t>
+  </si>
+  <si>
+    <t>03/18/26 15:01 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 16:30 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 22:24 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 23:40 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi W of Raytown MO</t>
+  </si>
+  <si>
+    <t>03/18/26 23:44 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi N of Grandview MO</t>
+  </si>
+  <si>
+    <t>03/19/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>6.8mi SW of Vinita OK</t>
+  </si>
+  <si>
+    <t>03/19/26 09:40 EDT</t>
+  </si>
+  <si>
+    <t>11.9mi N of Pryor Creek OK</t>
+  </si>
+  <si>
+    <t>03/19/26 09:41 EDT</t>
+  </si>
+  <si>
+    <t>10.4mi N of Pryor Creek OK</t>
+  </si>
+  <si>
+    <t>03/19/26 09:56 EDT</t>
+  </si>
+  <si>
+    <t>3mi SW of Pryor Creek OK</t>
+  </si>
+  <si>
+    <t>03/19/26 10:12 EDT</t>
+  </si>
+  <si>
+    <t>10.3mi S of Pryor Creek OK</t>
+  </si>
+  <si>
+    <t>03/19/26 10:55 EDT</t>
+  </si>
+  <si>
+    <t>0.4mi N of Grain Valley MO</t>
+  </si>
+  <si>
+    <t>03/20/26 07:32 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:57 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi NW of Muskogee OK</t>
+  </si>
+  <si>
+    <t>03/19/26 11:32 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 13:32 EDT</t>
+  </si>
+  <si>
+    <t>11.5mi N of Wagoner OK</t>
+  </si>
+  <si>
+    <t>03/19/26 14:00 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi SW of Pryor Creek OK</t>
+  </si>
+  <si>
+    <t>03/19/26 14:23 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 07:34 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 14:24 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 15:39 EDT</t>
+  </si>
+  <si>
+    <t>4mi NE of Shawnee KS</t>
+  </si>
+  <si>
+    <t>03/19/26 15:41 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 15:43 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>13.2mi N of Carthage MO</t>
+  </si>
+  <si>
+    <t>03/19/26 16:28 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 17:19 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 17:24 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 18:29 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 18:31 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 18:32 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi N of Shawnee KS</t>
+  </si>
+  <si>
+    <t>03/19/26 18:42 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi NW of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/19/26 18:43 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi NW of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/19/26 19:02 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 19:03 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 19:07 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 20:22 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 20:36 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 07:40 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 20:49 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi NW of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/19/26 21:04 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi SE of Bonner Springs KS</t>
+  </si>
+  <si>
+    <t>03/19/26 22:04 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 23:49 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 00:03 EDT</t>
   </si>
   <si>
     <t>4.4mi SE of Kansas City MO</t>
   </si>
   <si>
-    <t>03/13/26 12:06 EDT</t>
-  </si>
-  <si>
-    <t>3.7mi N of Spring Hill KS</t>
-  </si>
-  <si>
-    <t>03/13/26 13:08 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 14:01 EDT</t>
-  </si>
-  <si>
-    <t>4.7mi E of Roeland Park KS</t>
-  </si>
-  <si>
-    <t>03/13/26 14:44 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 14:46 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 17:35 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 19:01 EDT</t>
-  </si>
-  <si>
-    <t>2.3mi NW of Raytown MO</t>
-  </si>
-  <si>
-    <t>03/13/26 20:15 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 20:39 EDT</t>
-  </si>
-  <si>
-    <t>03/13/26 20:51 EDT</t>
-  </si>
-  <si>
-    <t>2.2mi SE of Lenexa KS</t>
-  </si>
-  <si>
-    <t>03/13/26 21:19 EDT</t>
-  </si>
-  <si>
-    <t>1.4mi S of Olathe KS</t>
-  </si>
-  <si>
-    <t>03/13/26 22:04 EDT</t>
-  </si>
-  <si>
-    <t>03/14/26 02:18 EDT</t>
+    <t>03/20/26 00:07 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 00:19 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 00:49 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 10:36 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:08 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi SE of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/20/26 11:24 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:14 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:39 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:41 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:42 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:50 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:55 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 13:21 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 14:07 EDT</t>
+  </si>
+  <si>
+    <t>2.1mi SW of Kansas City KS</t>
+  </si>
+  <si>
+    <t>03/20/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi N of Overland Park KS</t>
+  </si>
+  <si>
+    <t>03/20/26 15:23 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi E of Lenexa KS</t>
   </si>
 </sst>
 </file>
@@ -5511,7 +5853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1046"/>
+  <dimension ref="A1:M1121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -6052,19 +6394,17 @@
         <v>56</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3">
+        <v>339117157</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="3">
-        <v>567</v>
-      </c>
-      <c r="D21" s="3">
-        <v>339117505</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -6081,14 +6421,16 @@
         <v>56</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="C22" s="3">
+        <v>567</v>
+      </c>
       <c r="D22" s="3">
-        <v>339117157</v>
+        <v>339117505</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>59</v>
@@ -7588,7 +7930,7 @@
         <v>151</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C75" s="3">
         <v>567</v>
@@ -7625,7 +7967,7 @@
         <v>155</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C76" s="3">
         <v>567</v>
@@ -7654,7 +7996,7 @@
         <v>157</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C77" s="3">
         <v>567</v>
@@ -7683,7 +8025,7 @@
         <v>159</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C78" s="3">
         <v>567</v>
@@ -7712,7 +8054,7 @@
         <v>161</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C79" s="3">
         <v>567</v>
@@ -7741,7 +8083,7 @@
         <v>163</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C80" s="3">
         <v>567</v>
@@ -7770,7 +8112,7 @@
         <v>165</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C81" s="3">
         <v>567</v>
@@ -7911,7 +8253,7 @@
         <v>173</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C86" s="3">
         <v>567</v>
@@ -7946,7 +8288,7 @@
         <v>176</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C87" s="3">
         <v>567</v>
@@ -8060,7 +8402,7 @@
         <v>183</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C91" s="3">
         <v>567</v>
@@ -8089,7 +8431,7 @@
         <v>184</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C92" s="3">
         <v>567</v>
@@ -8118,7 +8460,7 @@
         <v>186</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C93" s="3">
         <v>567</v>
@@ -8147,7 +8489,7 @@
         <v>187</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C94" s="3">
         <v>567</v>
@@ -8176,7 +8518,7 @@
         <v>188</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C95" s="3">
         <v>567</v>
@@ -8205,7 +8547,7 @@
         <v>190</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C96" s="3">
         <v>567</v>
@@ -8234,7 +8576,7 @@
         <v>192</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C97" s="3">
         <v>567</v>
@@ -8319,7 +8661,7 @@
         <v>198</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C100" s="3">
         <v>567</v>
@@ -8348,7 +8690,7 @@
         <v>200</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C101" s="3">
         <v>567</v>
@@ -8377,7 +8719,7 @@
         <v>202</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C102" s="3">
         <v>567</v>
@@ -8406,7 +8748,7 @@
         <v>203</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C103" s="3">
         <v>567</v>
@@ -8435,7 +8777,7 @@
         <v>205</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C104" s="3">
         <v>567</v>
@@ -8464,7 +8806,7 @@
         <v>207</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C105" s="3">
         <v>567</v>
@@ -8493,7 +8835,7 @@
         <v>209</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C106" s="3">
         <v>567</v>
@@ -8522,7 +8864,7 @@
         <v>211</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C107" s="3">
         <v>567</v>
@@ -8551,7 +8893,7 @@
         <v>213</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C108" s="3">
         <v>567</v>
@@ -8580,7 +8922,7 @@
         <v>215</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C109" s="3">
         <v>567</v>
@@ -8609,7 +8951,7 @@
         <v>217</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C110" s="3">
         <v>567</v>
@@ -8665,7 +9007,7 @@
         <v>219</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C112" s="3">
         <v>567</v>
@@ -8694,7 +9036,7 @@
         <v>221</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C113" s="3">
         <v>567</v>
@@ -8723,7 +9065,7 @@
         <v>223</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C114" s="3">
         <v>567</v>
@@ -8752,7 +9094,7 @@
         <v>225</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C115" s="3">
         <v>567</v>
@@ -8783,7 +9125,7 @@
         <v>227</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C116" s="3">
         <v>567</v>
@@ -8814,7 +9156,7 @@
         <v>229</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C117" s="3">
         <v>567</v>
@@ -8901,7 +9243,7 @@
         <v>235</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C120" s="3">
         <v>567</v>
@@ -8930,7 +9272,7 @@
         <v>237</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C121" s="3">
         <v>567</v>
@@ -9813,7 +10155,7 @@
         <v>291</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C152" s="3">
         <v>567</v>
@@ -9850,7 +10192,7 @@
         <v>295</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C153" s="3">
         <v>567</v>
@@ -9914,7 +10256,7 @@
         <v>301</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C155" s="3">
         <v>567</v>
@@ -10090,7 +10432,7 @@
         <v>313</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C161" s="3">
         <v>567</v>
@@ -10127,7 +10469,7 @@
         <v>317</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C162" s="3">
         <v>567</v>
@@ -10156,7 +10498,7 @@
         <v>319</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C163" s="3">
         <v>567</v>
@@ -10185,7 +10527,7 @@
         <v>320</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C164" s="3">
         <v>567</v>
@@ -10214,7 +10556,7 @@
         <v>321</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C165" s="3">
         <v>567</v>
@@ -10243,7 +10585,7 @@
         <v>323</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C166" s="3">
         <v>567</v>
@@ -10272,7 +10614,7 @@
         <v>324</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C167" s="3">
         <v>567</v>
@@ -10593,7 +10935,7 @@
         <v>345</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C178" s="3">
         <v>567</v>
@@ -10628,7 +10970,7 @@
         <v>348</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C179" s="3">
         <v>567</v>
@@ -10657,7 +10999,7 @@
         <v>350</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C180" s="3">
         <v>567</v>
@@ -10686,7 +11028,7 @@
         <v>351</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C181" s="3">
         <v>567</v>
@@ -10715,7 +11057,7 @@
         <v>353</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C182" s="3">
         <v>567</v>
@@ -10746,7 +11088,7 @@
         <v>355</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C183" s="3">
         <v>567</v>
@@ -10775,7 +11117,7 @@
         <v>357</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C184" s="3">
         <v>567</v>
@@ -11380,7 +11722,7 @@
         <v>391</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C205" s="3">
         <v>567</v>
@@ -12020,7 +12362,7 @@
         <v>433</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C227" s="3">
         <v>567</v>
@@ -12049,7 +12391,7 @@
         <v>435</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C228" s="3">
         <v>567</v>
@@ -14579,7 +14921,7 @@
         <v>568</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C314" s="3">
         <v>567</v>
@@ -14616,7 +14958,7 @@
         <v>572</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C315" s="3">
         <v>567</v>
@@ -14798,7 +15140,7 @@
         <v>583</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C321" s="3">
         <v>567</v>
@@ -14827,7 +15169,7 @@
         <v>584</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C322" s="3">
         <v>567</v>
@@ -14916,7 +15258,7 @@
         <v>587</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C325" s="3">
         <v>567</v>
@@ -15123,7 +15465,7 @@
         <v>597</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C332" s="3">
         <v>567</v>
@@ -18811,7 +19153,7 @@
         <v>812</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C458" s="3">
         <v>567</v>
@@ -19404,7 +19746,7 @@
         <v>846</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C479" s="3">
         <v>567</v>
@@ -19468,7 +19810,7 @@
         <v>851</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C481" s="3">
         <v>567</v>
@@ -20396,10 +20738,10 @@
         <v>566</v>
       </c>
       <c r="D513" s="3">
-        <v>347989481</v>
+        <v>347989482</v>
       </c>
       <c r="E513" s="3" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="F513" s="3" t="s">
         <v>900</v>
@@ -20425,10 +20767,10 @@
         <v>566</v>
       </c>
       <c r="D514" s="3">
-        <v>347989482</v>
+        <v>347989481</v>
       </c>
       <c r="E514" s="3" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="F514" s="3" t="s">
         <v>900</v>
@@ -22032,7 +22374,7 @@
         <v>993</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C569" s="3">
         <v>567</v>
@@ -22090,7 +22432,7 @@
         <v>995</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C571" s="3">
         <v>567</v>
@@ -22179,7 +22521,7 @@
         <v>1001</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C574" s="3">
         <v>567</v>
@@ -22262,7 +22604,7 @@
         <v>1005</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C577" s="3">
         <v>567</v>
@@ -22515,7 +22857,7 @@
         <v>1017</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C586" s="3">
         <v>567</v>
@@ -22544,7 +22886,7 @@
         <v>1018</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C587" s="3">
         <v>567</v>
@@ -22840,7 +23182,7 @@
         <v>1038</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C597" s="3">
         <v>567</v>
@@ -22927,7 +23269,7 @@
         <v>1043</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C600" s="3">
         <v>567</v>
@@ -26289,7 +26631,7 @@
         <v>1218</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C716" s="3">
         <v>567</v>
@@ -28564,7 +28906,7 @@
         <v>1348</v>
       </c>
       <c r="B795" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C795" s="3">
         <v>567</v>
@@ -28904,7 +29246,7 @@
         <v>1361</v>
       </c>
       <c r="B807" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C807" s="3">
         <v>567</v>
@@ -28941,7 +29283,7 @@
         <v>1365</v>
       </c>
       <c r="B808" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C808" s="3">
         <v>567</v>
@@ -29115,7 +29457,7 @@
         <v>1373</v>
       </c>
       <c r="B814" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C814" s="3">
         <v>567</v>
@@ -29144,7 +29486,7 @@
         <v>1374</v>
       </c>
       <c r="B815" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C815" s="3">
         <v>567</v>
@@ -29345,7 +29687,7 @@
         <v>1384</v>
       </c>
       <c r="B822" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C822" s="3">
         <v>567</v>
@@ -30902,7 +31244,7 @@
         <v>1454</v>
       </c>
       <c r="B877" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C877" s="3">
         <v>567</v>
@@ -31248,7 +31590,7 @@
         <v>1474</v>
       </c>
       <c r="B889" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C889" s="3">
         <v>567</v>
@@ -31671,7 +32013,7 @@
         <v>1498</v>
       </c>
       <c r="B904" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C904" s="3">
         <v>567</v>
@@ -31700,7 +32042,7 @@
         <v>1500</v>
       </c>
       <c r="B905" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C905" s="3">
         <v>567</v>
@@ -34101,7 +34443,7 @@
         <v>1620</v>
       </c>
       <c r="B988" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C988" s="3">
         <v>567</v>
@@ -34167,19 +34509,19 @@
         <v>1625</v>
       </c>
       <c r="B990" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C990" s="3">
         <v>567</v>
       </c>
       <c r="D990" s="3">
-        <v>357698711</v>
+        <v>357701534</v>
       </c>
       <c r="E990" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F990" s="3" t="s">
-        <v>18</v>
+        <v>1152</v>
       </c>
       <c r="G990" s="3"/>
       <c r="H990" s="3"/>
@@ -34196,19 +34538,19 @@
         <v>1626</v>
       </c>
       <c r="B991" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C991" s="3">
         <v>567</v>
       </c>
       <c r="D991" s="3">
-        <v>357701534</v>
+        <v>357702151</v>
       </c>
       <c r="E991" s="3" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="F991" s="3" t="s">
-        <v>1152</v>
+        <v>1627</v>
       </c>
       <c r="G991" s="3"/>
       <c r="H991" s="3"/>
@@ -34222,22 +34564,20 @@
     </row>
     <row r="992" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A992" s="3" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B992" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C992" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C992" s="3"/>
       <c r="D992" s="3">
-        <v>357702151</v>
+        <v>357825318</v>
       </c>
       <c r="E992" s="3" t="s">
-        <v>276</v>
+        <v>17</v>
       </c>
       <c r="F992" s="3" t="s">
-        <v>1628</v>
+        <v>21</v>
       </c>
       <c r="G992" s="3"/>
       <c r="H992" s="3"/>
@@ -34258,55 +34598,57 @@
       </c>
       <c r="C993" s="3"/>
       <c r="D993" s="3">
-        <v>357825318</v>
+        <v>357874261</v>
       </c>
       <c r="E993" s="3" t="s">
-        <v>17</v>
+        <v>296</v>
       </c>
       <c r="F993" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G993" s="3"/>
+        <v>1630</v>
+      </c>
+      <c r="G993" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H993" s="3"/>
       <c r="I993" s="3"/>
       <c r="J993" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K993" s="3"/>
-      <c r="L993" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K993" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L993" s="3" t="s">
+        <v>1631</v>
+      </c>
       <c r="M993" s="3"/>
     </row>
     <row r="994" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A994" s="3" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B994" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C994" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="C994" s="3">
+        <v>567</v>
+      </c>
       <c r="D994" s="3">
-        <v>357874261</v>
+        <v>358067409</v>
       </c>
       <c r="E994" s="3" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="F994" s="3" t="s">
-        <v>1631</v>
-      </c>
-      <c r="G994" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>1512</v>
+      </c>
+      <c r="G994" s="3"/>
       <c r="H994" s="3"/>
       <c r="I994" s="3"/>
       <c r="J994" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K994" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L994" s="3" t="s">
-        <v>1632</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K994" s="3"/>
+      <c r="L994" s="3"/>
       <c r="M994" s="3"/>
     </row>
     <row r="995" spans="1:13" x14ac:dyDescent="0.25">
@@ -34314,19 +34656,19 @@
         <v>1633</v>
       </c>
       <c r="B995" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C995" s="3">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D995" s="3">
-        <v>357898622</v>
+        <v>358067943</v>
       </c>
       <c r="E995" s="3" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="F995" s="3" t="s">
-        <v>1634</v>
+        <v>18</v>
       </c>
       <c r="G995" s="3"/>
       <c r="H995" s="3"/>
@@ -34340,22 +34682,20 @@
     </row>
     <row r="996" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A996" s="3" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B996" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C996" s="3">
-        <v>565</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C996" s="3"/>
       <c r="D996" s="3">
-        <v>357918896</v>
+        <v>358079040</v>
       </c>
       <c r="E996" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F996" s="3" t="s">
-        <v>1636</v>
+        <v>18</v>
       </c>
       <c r="G996" s="3"/>
       <c r="H996" s="3"/>
@@ -34369,22 +34709,20 @@
     </row>
     <row r="997" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A997" s="3" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="B997" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C997" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C997" s="3"/>
       <c r="D997" s="3">
-        <v>358016201</v>
+        <v>358093760</v>
       </c>
       <c r="E997" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F997" s="3" t="s">
-        <v>1437</v>
+        <v>1636</v>
       </c>
       <c r="G997" s="3"/>
       <c r="H997" s="3"/>
@@ -34398,22 +34736,20 @@
     </row>
     <row r="998" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" s="3" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B998" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C998" s="3">
-        <v>28</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C998" s="3"/>
       <c r="D998" s="3">
-        <v>358058901</v>
+        <v>358108167</v>
       </c>
       <c r="E998" s="3" t="s">
-        <v>1197</v>
+        <v>17</v>
       </c>
       <c r="F998" s="3" t="s">
-        <v>1639</v>
+        <v>18</v>
       </c>
       <c r="G998" s="3"/>
       <c r="H998" s="3"/>
@@ -34427,22 +34763,22 @@
     </row>
     <row r="999" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" s="3" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="B999" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C999" s="3">
-        <v>567</v>
+        <v>28</v>
       </c>
       <c r="D999" s="3">
-        <v>358059037</v>
+        <v>358115203</v>
       </c>
       <c r="E999" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F999" s="3" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="G999" s="3"/>
       <c r="H999" s="3"/>
@@ -34456,22 +34792,22 @@
     </row>
     <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" s="3" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="B1000" s="3" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="C1000" s="3">
-        <v>565</v>
+        <v>28</v>
       </c>
       <c r="D1000" s="3">
-        <v>358064300</v>
+        <v>358118058</v>
       </c>
       <c r="E1000" s="3" t="s">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="F1000" s="3" t="s">
-        <v>1643</v>
+        <v>823</v>
       </c>
       <c r="G1000" s="3"/>
       <c r="H1000" s="3"/>
@@ -34485,22 +34821,20 @@
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" s="3" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="B1001" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1001" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1001" s="3"/>
       <c r="D1001" s="3">
-        <v>358067409</v>
+        <v>358135024</v>
       </c>
       <c r="E1001" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F1001" s="3" t="s">
-        <v>1512</v>
+        <v>531</v>
       </c>
       <c r="G1001" s="3"/>
       <c r="H1001" s="3"/>
@@ -34514,25 +34848,27 @@
     </row>
     <row r="1002" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1002" s="3" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="B1002" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C1002" s="3">
-        <v>567</v>
+        <v>28</v>
       </c>
       <c r="D1002" s="3">
-        <v>358067943</v>
+        <v>358169096</v>
       </c>
       <c r="E1002" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F1002" s="3" t="s">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="G1002" s="3"/>
-      <c r="H1002" s="3"/>
+      <c r="H1002" s="3">
+        <v>16</v>
+      </c>
       <c r="I1002" s="3"/>
       <c r="J1002" s="3" t="s">
         <v>19</v>
@@ -34543,20 +34879,20 @@
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" s="3" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="B1003" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1003" s="3"/>
       <c r="D1003" s="3">
-        <v>358079040</v>
+        <v>358201470</v>
       </c>
       <c r="E1003" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F1003" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G1003" s="3"/>
       <c r="H1003" s="3"/>
@@ -34570,20 +34906,20 @@
     </row>
     <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" s="3" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="B1004" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1004" s="3"/>
       <c r="D1004" s="3">
-        <v>358093760</v>
+        <v>358386907</v>
       </c>
       <c r="E1004" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F1004" s="3" t="s">
-        <v>1648</v>
+        <v>47</v>
       </c>
       <c r="G1004" s="3"/>
       <c r="H1004" s="3"/>
@@ -34597,161 +34933,197 @@
     </row>
     <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" s="3" t="s">
-        <v>1649</v>
+        <v>1645</v>
       </c>
       <c r="B1005" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1005" s="3">
-        <v>566</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C1005" s="3"/>
       <c r="D1005" s="3">
-        <v>358097434</v>
+        <v>358432098</v>
       </c>
       <c r="E1005" s="3" t="s">
-        <v>276</v>
+        <v>609</v>
       </c>
       <c r="F1005" s="3" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G1005" s="3"/>
+        <v>1646</v>
+      </c>
+      <c r="G1005" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1005" s="3"/>
       <c r="I1005" s="3"/>
       <c r="J1005" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1005" s="3"/>
-      <c r="L1005" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1005" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1005" s="3" t="s">
+        <v>1623</v>
+      </c>
       <c r="M1005" s="3"/>
     </row>
     <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" s="3" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="B1006" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1006" s="3"/>
+        <v>432</v>
+      </c>
+      <c r="C1006" s="3">
+        <v>31</v>
+      </c>
       <c r="D1006" s="3">
-        <v>358108167</v>
+        <v>358475529</v>
       </c>
       <c r="E1006" s="3" t="s">
-        <v>17</v>
+        <v>296</v>
       </c>
       <c r="F1006" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1006" s="3"/>
+        <v>1648</v>
+      </c>
+      <c r="G1006" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1006" s="3"/>
       <c r="I1006" s="3"/>
       <c r="J1006" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1006" s="3"/>
-      <c r="L1006" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1006" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1006" s="3" t="s">
+        <v>1649</v>
+      </c>
       <c r="M1006" s="3"/>
     </row>
     <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" s="3" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B1007" s="3" t="s">
-        <v>27</v>
+        <v>432</v>
       </c>
       <c r="C1007" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D1007" s="3">
-        <v>358115203</v>
+        <v>358500729</v>
       </c>
       <c r="E1007" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F1007" s="3" t="s">
-        <v>1653</v>
-      </c>
-      <c r="G1007" s="3"/>
+        <v>692</v>
+      </c>
+      <c r="G1007" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1007" s="3"/>
       <c r="I1007" s="3"/>
       <c r="J1007" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1007" s="3"/>
-      <c r="L1007" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1007" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1007" s="3" t="s">
+        <v>1651</v>
+      </c>
       <c r="M1007" s="3"/>
     </row>
     <row r="1008" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1008" s="3" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="B1008" s="3" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C1008" s="3">
-        <v>28</v>
+        <v>567</v>
       </c>
       <c r="D1008" s="3">
-        <v>358118058</v>
+        <v>358503299</v>
       </c>
       <c r="E1008" s="3" t="s">
-        <v>50</v>
+        <v>449</v>
       </c>
       <c r="F1008" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="G1008" s="3"/>
+        <v>1653</v>
+      </c>
+      <c r="G1008" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1008" s="3"/>
       <c r="I1008" s="3"/>
       <c r="J1008" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1008" s="3"/>
-      <c r="L1008" s="3"/>
-      <c r="M1008" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1008" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1008" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="M1008" s="3" t="s">
+        <v>1655</v>
+      </c>
     </row>
     <row r="1009" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1009" s="3" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1009" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1009" s="3"/>
+        <v>432</v>
+      </c>
+      <c r="C1009" s="3">
+        <v>31</v>
+      </c>
       <c r="D1009" s="3">
-        <v>358135024</v>
+        <v>358510078</v>
       </c>
       <c r="E1009" s="3" t="s">
-        <v>17</v>
+        <v>296</v>
       </c>
       <c r="F1009" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="G1009" s="3"/>
+        <v>1414</v>
+      </c>
+      <c r="G1009" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1009" s="3"/>
       <c r="I1009" s="3"/>
       <c r="J1009" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1009" s="3"/>
-      <c r="L1009" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1009" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1009" s="3" t="s">
+        <v>1657</v>
+      </c>
       <c r="M1009" s="3"/>
     </row>
     <row r="1010" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1010" s="3" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B1010" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1010" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C1010" s="3">
+        <v>28</v>
+      </c>
       <c r="D1010" s="3">
-        <v>358136031</v>
+        <v>358513441</v>
       </c>
       <c r="E1010" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F1010" s="3" t="s">
-        <v>1570</v>
+        <v>692</v>
       </c>
       <c r="G1010" s="3"/>
       <c r="H1010" s="3"/>
@@ -34765,20 +35137,20 @@
     </row>
     <row r="1011" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1011" s="3" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B1011" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1011" s="3"/>
       <c r="D1011" s="3">
-        <v>358136061</v>
+        <v>358633471</v>
       </c>
       <c r="E1011" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F1011" s="3" t="s">
-        <v>686</v>
+        <v>21</v>
       </c>
       <c r="G1011" s="3"/>
       <c r="H1011" s="3"/>
@@ -34792,27 +35164,23 @@
     </row>
     <row r="1012" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1012" s="3" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B1012" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1012" s="3">
-        <v>28</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1012" s="3"/>
       <c r="D1012" s="3">
-        <v>358169096</v>
+        <v>358730579</v>
       </c>
       <c r="E1012" s="3" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F1012" s="3" t="s">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="G1012" s="3"/>
-      <c r="H1012" s="3">
-        <v>16</v>
-      </c>
+      <c r="H1012" s="3"/>
       <c r="I1012" s="3"/>
       <c r="J1012" s="3" t="s">
         <v>19</v>
@@ -34823,20 +35191,20 @@
     </row>
     <row r="1013" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1013" s="3" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B1013" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1013" s="3"/>
       <c r="D1013" s="3">
-        <v>358201470</v>
+        <v>358853510</v>
       </c>
       <c r="E1013" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F1013" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G1013" s="3"/>
       <c r="H1013" s="3"/>
@@ -34850,22 +35218,20 @@
     </row>
     <row r="1014" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1014" s="3" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B1014" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1014" s="3">
-        <v>28</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1014" s="3"/>
       <c r="D1014" s="3">
-        <v>358254745</v>
+        <v>358880498</v>
       </c>
       <c r="E1014" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F1014" s="3" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="G1014" s="3"/>
       <c r="H1014" s="3"/>
@@ -34879,51 +35245,59 @@
     </row>
     <row r="1015" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1015" s="3" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B1015" s="3" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C1015" s="3">
-        <v>566</v>
+        <v>28</v>
       </c>
       <c r="D1015" s="3">
-        <v>358353233</v>
+        <v>358896106</v>
       </c>
       <c r="E1015" s="3" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="F1015" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="G1015" s="3"/>
-      <c r="H1015" s="3"/>
-      <c r="I1015" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="G1015" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1015" s="3">
+        <v>16</v>
+      </c>
+      <c r="I1015" s="3">
+        <v>35</v>
+      </c>
       <c r="J1015" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1015" s="3"/>
-      <c r="L1015" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1015" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1015" s="3" t="s">
+        <v>1665</v>
+      </c>
       <c r="M1015" s="3"/>
     </row>
     <row r="1016" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="B1016" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1016" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1016" s="3"/>
       <c r="D1016" s="3">
-        <v>358374349</v>
+        <v>358899792</v>
       </c>
       <c r="E1016" s="3" t="s">
-        <v>449</v>
+        <v>17</v>
       </c>
       <c r="F1016" s="3" t="s">
-        <v>1664</v>
+        <v>47</v>
       </c>
       <c r="G1016" s="3"/>
       <c r="H1016" s="3"/>
@@ -34937,20 +35311,20 @@
     </row>
     <row r="1017" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" s="3" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B1017" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1017" s="3"/>
       <c r="D1017" s="3">
-        <v>358386907</v>
+        <v>358902432</v>
       </c>
       <c r="E1017" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F1017" s="3" t="s">
-        <v>47</v>
+        <v>1668</v>
       </c>
       <c r="G1017" s="3"/>
       <c r="H1017" s="3"/>
@@ -34964,22 +35338,22 @@
     </row>
     <row r="1018" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1018" s="3" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="B1018" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C1018" s="3">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D1018" s="3">
-        <v>358402582</v>
+        <v>358906153</v>
       </c>
       <c r="E1018" s="3" t="s">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="F1018" s="3" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="G1018" s="3"/>
       <c r="H1018" s="3"/>
@@ -34993,20 +35367,22 @@
     </row>
     <row r="1019" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" s="3" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="B1019" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C1019" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="C1019" s="3">
+        <v>567</v>
+      </c>
       <c r="D1019" s="3">
-        <v>358432035</v>
+        <v>358909950</v>
       </c>
       <c r="E1019" s="3" t="s">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="F1019" s="3" t="s">
-        <v>1669</v>
+        <v>88</v>
       </c>
       <c r="G1019" s="3"/>
       <c r="H1019" s="3"/>
@@ -35020,98 +35396,78 @@
     </row>
     <row r="1020" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1020" s="3" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="B1020" s="3" t="s">
-        <v>309</v>
+        <v>16</v>
       </c>
       <c r="C1020" s="3"/>
       <c r="D1020" s="3">
-        <v>358432098</v>
+        <v>358926010</v>
       </c>
       <c r="E1020" s="3" t="s">
-        <v>609</v>
+        <v>17</v>
       </c>
       <c r="F1020" s="3" t="s">
-        <v>1669</v>
-      </c>
-      <c r="G1020" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G1020" s="3"/>
       <c r="H1020" s="3"/>
       <c r="I1020" s="3"/>
       <c r="J1020" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1020" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1020" s="3" t="s">
-        <v>1623</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K1020" s="3"/>
+      <c r="L1020" s="3"/>
       <c r="M1020" s="3"/>
     </row>
     <row r="1021" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1021" s="3" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="B1021" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C1021" s="3">
-        <v>31</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1021" s="3"/>
       <c r="D1021" s="3">
-        <v>358475529</v>
+        <v>358950494</v>
       </c>
       <c r="E1021" s="3" t="s">
-        <v>296</v>
+        <v>17</v>
       </c>
       <c r="F1021" s="3" t="s">
-        <v>1671</v>
-      </c>
-      <c r="G1021" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G1021" s="3"/>
       <c r="H1021" s="3"/>
       <c r="I1021" s="3"/>
       <c r="J1021" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1021" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1021" s="3" t="s">
-        <v>1672</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K1021" s="3"/>
+      <c r="L1021" s="3"/>
       <c r="M1021" s="3"/>
     </row>
     <row r="1022" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1022" s="3" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1022" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1022" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1022" s="3"/>
       <c r="D1022" s="3">
-        <v>358500185</v>
+        <v>359016483</v>
       </c>
       <c r="E1022" s="3" t="s">
-        <v>449</v>
+        <v>17</v>
       </c>
       <c r="F1022" s="3" t="s">
-        <v>1674</v>
+        <v>18</v>
       </c>
       <c r="G1022" s="3"/>
-      <c r="H1022" s="3">
-        <v>70</v>
-      </c>
-      <c r="I1022" s="3">
-        <v>65</v>
-      </c>
+      <c r="H1022" s="3"/>
+      <c r="I1022" s="3"/>
       <c r="J1022" s="3" t="s">
         <v>19</v>
       </c>
@@ -35124,54 +35480,44 @@
         <v>1675</v>
       </c>
       <c r="B1023" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C1023" s="3">
-        <v>31</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1023" s="3"/>
       <c r="D1023" s="3">
-        <v>358500729</v>
+        <v>359025197</v>
       </c>
       <c r="E1023" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F1023" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="G1023" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G1023" s="3"/>
       <c r="H1023" s="3"/>
       <c r="I1023" s="3"/>
       <c r="J1023" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1023" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1023" s="3" t="s">
-        <v>1676</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K1023" s="3"/>
+      <c r="L1023" s="3"/>
       <c r="M1023" s="3"/>
     </row>
     <row r="1024" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1024" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B1024" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1024" s="3"/>
+      <c r="D1024" s="3">
+        <v>359028651</v>
+      </c>
+      <c r="E1024" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1024" s="3" t="s">
         <v>1677</v>
-      </c>
-      <c r="B1024" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1024" s="3">
-        <v>567</v>
-      </c>
-      <c r="D1024" s="3">
-        <v>358503299</v>
-      </c>
-      <c r="E1024" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="F1024" s="3" t="s">
-        <v>1678</v>
       </c>
       <c r="G1024" s="3"/>
       <c r="H1024" s="3"/>
@@ -35185,22 +35531,20 @@
     </row>
     <row r="1025" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1025" s="3" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B1025" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C1025" s="3">
-        <v>31</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1025" s="3"/>
       <c r="D1025" s="3">
-        <v>358510078</v>
+        <v>359033138</v>
       </c>
       <c r="E1025" s="3" t="s">
-        <v>296</v>
+        <v>17</v>
       </c>
       <c r="F1025" s="3" t="s">
-        <v>1414</v>
+        <v>47</v>
       </c>
       <c r="G1025" s="3"/>
       <c r="H1025" s="3"/>
@@ -35214,22 +35558,20 @@
     </row>
     <row r="1026" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1026" s="3" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B1026" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1026" s="3">
-        <v>28</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1026" s="3"/>
       <c r="D1026" s="3">
-        <v>358513441</v>
+        <v>359034972</v>
       </c>
       <c r="E1026" s="3" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F1026" s="3" t="s">
-        <v>692</v>
+        <v>263</v>
       </c>
       <c r="G1026" s="3"/>
       <c r="H1026" s="3"/>
@@ -35243,20 +35585,20 @@
     </row>
     <row r="1027" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1027" s="3" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1027" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1027" s="3"/>
       <c r="D1027" s="3">
-        <v>358633471</v>
+        <v>359049131</v>
       </c>
       <c r="E1027" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F1027" s="3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G1027" s="3"/>
       <c r="H1027" s="3"/>
@@ -35270,47 +35612,57 @@
     </row>
     <row r="1028" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1028" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1028" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1028" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1028" s="3">
+        <v>359082130</v>
+      </c>
+      <c r="E1028" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1028" s="3" t="s">
         <v>1682</v>
       </c>
-      <c r="B1028" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1028" s="3"/>
-      <c r="D1028" s="3">
-        <v>358653297</v>
-      </c>
-      <c r="E1028" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1028" s="3" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G1028" s="3"/>
-      <c r="H1028" s="3"/>
+      <c r="G1028" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1028" s="3">
+        <v>55</v>
+      </c>
       <c r="I1028" s="3"/>
       <c r="J1028" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1028" s="3"/>
-      <c r="L1028" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1028" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1028" s="3" t="s">
+        <v>1683</v>
+      </c>
       <c r="M1028" s="3"/>
     </row>
     <row r="1029" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1029" s="3" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1029" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1029" s="3"/>
       <c r="D1029" s="3">
-        <v>358653683</v>
+        <v>359086236</v>
       </c>
       <c r="E1029" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F1029" s="3" t="s">
-        <v>1684</v>
+        <v>21</v>
       </c>
       <c r="G1029" s="3"/>
       <c r="H1029" s="3"/>
@@ -35324,49 +35676,57 @@
     </row>
     <row r="1030" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1030" s="3" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B1030" s="3" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="C1030" s="3">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D1030" s="3">
-        <v>358653806</v>
+        <v>359102469</v>
       </c>
       <c r="E1030" s="3" t="s">
-        <v>609</v>
+        <v>34</v>
       </c>
       <c r="F1030" s="3" t="s">
-        <v>1685</v>
-      </c>
-      <c r="G1030" s="3"/>
+        <v>1686</v>
+      </c>
+      <c r="G1030" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1030" s="3"/>
       <c r="I1030" s="3"/>
       <c r="J1030" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1030" s="3"/>
-      <c r="L1030" s="3"/>
-      <c r="M1030" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1030" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1030" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="M1030" s="3" t="s">
+        <v>1655</v>
+      </c>
     </row>
     <row r="1031" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1031" s="3" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B1031" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C1031" s="3"/>
       <c r="D1031" s="3">
-        <v>358654044</v>
+        <v>359125640</v>
       </c>
       <c r="E1031" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F1031" s="3" t="s">
-        <v>1687</v>
+        <v>21</v>
       </c>
       <c r="G1031" s="3"/>
       <c r="H1031" s="3"/>
@@ -35380,20 +35740,22 @@
     </row>
     <row r="1032" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1032" s="3" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1032" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1032" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C1032" s="3">
+        <v>28</v>
+      </c>
       <c r="D1032" s="3">
-        <v>358672748</v>
+        <v>359130017</v>
       </c>
       <c r="E1032" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F1032" s="3" t="s">
-        <v>1689</v>
+        <v>692</v>
       </c>
       <c r="G1032" s="3"/>
       <c r="H1032" s="3"/>
@@ -35410,19 +35772,17 @@
         <v>1690</v>
       </c>
       <c r="B1033" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1033" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1033" s="3"/>
       <c r="D1033" s="3">
-        <v>358676564</v>
+        <v>359145480</v>
       </c>
       <c r="E1033" s="3" t="s">
-        <v>276</v>
+        <v>17</v>
       </c>
       <c r="F1033" s="3" t="s">
-        <v>1691</v>
+        <v>21</v>
       </c>
       <c r="G1033" s="3"/>
       <c r="H1033" s="3"/>
@@ -35436,22 +35796,22 @@
     </row>
     <row r="1034" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1034" s="3" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B1034" s="3" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="C1034" s="3">
-        <v>565</v>
+        <v>28</v>
       </c>
       <c r="D1034" s="3">
-        <v>358701691</v>
+        <v>359151454</v>
       </c>
       <c r="E1034" s="3" t="s">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="F1034" s="3" t="s">
-        <v>1693</v>
+        <v>692</v>
       </c>
       <c r="G1034" s="3"/>
       <c r="H1034" s="3"/>
@@ -35465,20 +35825,22 @@
     </row>
     <row r="1035" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1035" s="3" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="B1035" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1035" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C1035" s="3">
+        <v>28</v>
+      </c>
       <c r="D1035" s="3">
-        <v>358730579</v>
+        <v>359158378</v>
       </c>
       <c r="E1035" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F1035" s="3" t="s">
-        <v>18</v>
+        <v>692</v>
       </c>
       <c r="G1035" s="3"/>
       <c r="H1035" s="3"/>
@@ -35492,20 +35854,20 @@
     </row>
     <row r="1036" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1036" s="3" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B1036" s="3" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="C1036" s="3"/>
       <c r="D1036" s="3">
-        <v>358755938</v>
+        <v>359266799</v>
       </c>
       <c r="E1036" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F1036" s="3" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="G1036" s="3"/>
       <c r="H1036" s="3"/>
@@ -35519,47 +35881,59 @@
     </row>
     <row r="1037" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1037" s="3" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="B1037" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C1037" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="C1037" s="3">
+        <v>567</v>
+      </c>
       <c r="D1037" s="3">
-        <v>358777865</v>
+        <v>359329734</v>
       </c>
       <c r="E1037" s="3" t="s">
-        <v>34</v>
+        <v>449</v>
       </c>
       <c r="F1037" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="G1037" s="3"/>
+        <v>1696</v>
+      </c>
+      <c r="G1037" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H1037" s="3"/>
       <c r="I1037" s="3"/>
       <c r="J1037" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1037" s="3"/>
-      <c r="L1037" s="3"/>
-      <c r="M1037" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="K1037" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1037" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="M1037" s="3" t="s">
+        <v>1698</v>
+      </c>
     </row>
     <row r="1038" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1038" s="3" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1038" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C1038" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="C1038" s="3">
+        <v>566</v>
+      </c>
       <c r="D1038" s="3">
-        <v>358778248</v>
+        <v>359486562</v>
       </c>
       <c r="E1038" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F1038" s="3" t="s">
-        <v>322</v>
+        <v>1700</v>
       </c>
       <c r="G1038" s="3"/>
       <c r="H1038" s="3"/>
@@ -35573,20 +35947,22 @@
     </row>
     <row r="1039" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1039" s="3" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="B1039" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1039" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C1039" s="3">
+        <v>28</v>
+      </c>
       <c r="D1039" s="3">
-        <v>358853510</v>
+        <v>359486916</v>
       </c>
       <c r="E1039" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F1039" s="3" t="s">
-        <v>18</v>
+        <v>692</v>
       </c>
       <c r="G1039" s="3"/>
       <c r="H1039" s="3"/>
@@ -35600,20 +35976,22 @@
     </row>
     <row r="1040" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1040" s="3" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="B1040" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1040" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C1040" s="3">
+        <v>28</v>
+      </c>
       <c r="D1040" s="3">
-        <v>358880498</v>
+        <v>359493055</v>
       </c>
       <c r="E1040" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F1040" s="3" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="G1040" s="3"/>
       <c r="H1040" s="3"/>
@@ -35627,30 +36005,26 @@
     </row>
     <row r="1041" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1041" s="3" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="B1041" s="3" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C1041" s="3">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="D1041" s="3">
-        <v>358896106</v>
+        <v>359493844</v>
       </c>
       <c r="E1041" s="3" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="F1041" s="3" t="s">
-        <v>74</v>
+        <v>1705</v>
       </c>
       <c r="G1041" s="3"/>
-      <c r="H1041" s="3">
-        <v>16</v>
-      </c>
-      <c r="I1041" s="3">
-        <v>35</v>
-      </c>
+      <c r="H1041" s="3"/>
+      <c r="I1041" s="3"/>
       <c r="J1041" s="3" t="s">
         <v>19</v>
       </c>
@@ -35660,20 +36034,22 @@
     </row>
     <row r="1042" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1042" s="3" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="B1042" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1042" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="C1042" s="3">
+        <v>566</v>
+      </c>
       <c r="D1042" s="3">
-        <v>358899792</v>
+        <v>359497241</v>
       </c>
       <c r="E1042" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F1042" s="3" t="s">
-        <v>47</v>
+        <v>1707</v>
       </c>
       <c r="G1042" s="3"/>
       <c r="H1042" s="3"/>
@@ -35687,20 +36063,22 @@
     </row>
     <row r="1043" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1043" s="3" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="B1043" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1043" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="C1043" s="3">
+        <v>567</v>
+      </c>
       <c r="D1043" s="3">
-        <v>358902432</v>
+        <v>359498270</v>
       </c>
       <c r="E1043" s="3" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F1043" s="3" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="G1043" s="3"/>
       <c r="H1043" s="3"/>
@@ -35714,22 +36092,22 @@
     </row>
     <row r="1044" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1044" s="3" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="B1044" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C1044" s="3">
-        <v>567</v>
+        <v>28</v>
       </c>
       <c r="D1044" s="3">
-        <v>358906153</v>
+        <v>359498573</v>
       </c>
       <c r="E1044" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F1044" s="3" t="s">
-        <v>1707</v>
+        <v>692</v>
       </c>
       <c r="G1044" s="3"/>
       <c r="H1044" s="3"/>
@@ -35743,22 +36121,20 @@
     </row>
     <row r="1045" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1045" s="3" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="B1045" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1045" s="3">
-        <v>567</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C1045" s="3"/>
       <c r="D1045" s="3">
-        <v>358909950</v>
+        <v>359615301</v>
       </c>
       <c r="E1045" s="3" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F1045" s="3" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G1045" s="3"/>
       <c r="H1045" s="3"/>
@@ -35772,20 +36148,22 @@
     </row>
     <row r="1046" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1046" s="3" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="B1046" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1046" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="C1046" s="3">
+        <v>566</v>
+      </c>
       <c r="D1046" s="3">
-        <v>358926010</v>
+        <v>359773397</v>
       </c>
       <c r="E1046" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F1046" s="3" t="s">
-        <v>18</v>
+        <v>606</v>
       </c>
       <c r="G1046" s="3"/>
       <c r="H1046" s="3"/>
@@ -35797,6 +36175,2149 @@
       <c r="L1046" s="3"/>
       <c r="M1046" s="3"/>
     </row>
+    <row r="1047" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1047" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B1047" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1047" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1047" s="3">
+        <v>359835449</v>
+      </c>
+      <c r="E1047" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1047" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G1047" s="3"/>
+      <c r="H1047" s="3"/>
+      <c r="I1047" s="3"/>
+      <c r="J1047" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1047" s="3"/>
+      <c r="L1047" s="3"/>
+      <c r="M1047" s="3"/>
+    </row>
+    <row r="1048" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1048" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B1048" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1048" s="3"/>
+      <c r="D1048" s="3">
+        <v>359906112</v>
+      </c>
+      <c r="E1048" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1048" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1048" s="3"/>
+      <c r="H1048" s="3"/>
+      <c r="I1048" s="3"/>
+      <c r="J1048" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1048" s="3"/>
+      <c r="L1048" s="3"/>
+      <c r="M1048" s="3"/>
+    </row>
+    <row r="1049" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1049" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1049" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1049" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1049" s="3">
+        <v>359934828</v>
+      </c>
+      <c r="E1049" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1049" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="G1049" s="3"/>
+      <c r="H1049" s="3"/>
+      <c r="I1049" s="3"/>
+      <c r="J1049" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1049" s="3"/>
+      <c r="L1049" s="3"/>
+      <c r="M1049" s="3"/>
+    </row>
+    <row r="1050" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1050" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B1050" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1050" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1050" s="3">
+        <v>359948925</v>
+      </c>
+      <c r="E1050" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1050" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1050" s="3"/>
+      <c r="H1050" s="3"/>
+      <c r="I1050" s="3"/>
+      <c r="J1050" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1050" s="3"/>
+      <c r="L1050" s="3"/>
+      <c r="M1050" s="3"/>
+    </row>
+    <row r="1051" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1051" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1051" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1051" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1051" s="3">
+        <v>359956615</v>
+      </c>
+      <c r="E1051" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1051" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="G1051" s="3"/>
+      <c r="H1051" s="3"/>
+      <c r="I1051" s="3"/>
+      <c r="J1051" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1051" s="3"/>
+      <c r="L1051" s="3"/>
+      <c r="M1051" s="3"/>
+    </row>
+    <row r="1052" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1052" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B1052" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1052" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1052" s="3">
+        <v>359988238</v>
+      </c>
+      <c r="E1052" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1052" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G1052" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1052" s="3"/>
+      <c r="I1052" s="3"/>
+      <c r="J1052" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1052" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1052" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="M1052" s="3"/>
+    </row>
+    <row r="1053" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1053" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1053" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1053" s="3"/>
+      <c r="D1053" s="3">
+        <v>360078973</v>
+      </c>
+      <c r="E1053" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1053" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1053" s="3"/>
+      <c r="H1053" s="3"/>
+      <c r="I1053" s="3"/>
+      <c r="J1053" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1053" s="3"/>
+      <c r="L1053" s="3"/>
+      <c r="M1053" s="3"/>
+    </row>
+    <row r="1054" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1054" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1054" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1054" s="3"/>
+      <c r="D1054" s="3">
+        <v>360105111</v>
+      </c>
+      <c r="E1054" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1054" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G1054" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1054" s="3"/>
+      <c r="I1054" s="3"/>
+      <c r="J1054" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1054" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1054" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="M1054" s="3"/>
+    </row>
+    <row r="1055" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1055" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1055" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1055" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1055" s="3">
+        <v>360109244</v>
+      </c>
+      <c r="E1055" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1055" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1055" s="3"/>
+      <c r="H1055" s="3"/>
+      <c r="I1055" s="3"/>
+      <c r="J1055" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1055" s="3"/>
+      <c r="L1055" s="3"/>
+      <c r="M1055" s="3"/>
+    </row>
+    <row r="1056" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1056" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1056" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1056" s="3"/>
+      <c r="D1056" s="3">
+        <v>360110752</v>
+      </c>
+      <c r="E1056" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1056" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G1056" s="3"/>
+      <c r="H1056" s="3"/>
+      <c r="I1056" s="3"/>
+      <c r="J1056" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1056" s="3"/>
+      <c r="L1056" s="3"/>
+      <c r="M1056" s="3"/>
+    </row>
+    <row r="1057" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1057" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1057" s="3"/>
+      <c r="D1057" s="3">
+        <v>360112117</v>
+      </c>
+      <c r="E1057" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1057" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="G1057" s="3"/>
+      <c r="H1057" s="3"/>
+      <c r="I1057" s="3"/>
+      <c r="J1057" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1057" s="3"/>
+      <c r="L1057" s="3"/>
+      <c r="M1057" s="3"/>
+    </row>
+    <row r="1058" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1058" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1058" s="3"/>
+      <c r="D1058" s="3">
+        <v>360112961</v>
+      </c>
+      <c r="E1058" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1058" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1058" s="3"/>
+      <c r="H1058" s="3"/>
+      <c r="I1058" s="3"/>
+      <c r="J1058" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1058" s="3"/>
+      <c r="L1058" s="3"/>
+      <c r="M1058" s="3"/>
+    </row>
+    <row r="1059" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1059" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B1059" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1059" s="3"/>
+      <c r="D1059" s="3">
+        <v>360113234</v>
+      </c>
+      <c r="E1059" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1059" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G1059" s="3"/>
+      <c r="H1059" s="3"/>
+      <c r="I1059" s="3"/>
+      <c r="J1059" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1059" s="3"/>
+      <c r="L1059" s="3"/>
+      <c r="M1059" s="3"/>
+    </row>
+    <row r="1060" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1060" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B1060" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1060" s="3"/>
+      <c r="D1060" s="3">
+        <v>360113816</v>
+      </c>
+      <c r="E1060" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1060" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="G1060" s="3"/>
+      <c r="H1060" s="3"/>
+      <c r="I1060" s="3"/>
+      <c r="J1060" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1060" s="3"/>
+      <c r="L1060" s="3"/>
+      <c r="M1060" s="3"/>
+    </row>
+    <row r="1061" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1061" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B1061" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1061" s="3"/>
+      <c r="D1061" s="3">
+        <v>360114219</v>
+      </c>
+      <c r="E1061" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1061" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G1061" s="3"/>
+      <c r="H1061" s="3"/>
+      <c r="I1061" s="3"/>
+      <c r="J1061" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1061" s="3"/>
+      <c r="L1061" s="3"/>
+      <c r="M1061" s="3"/>
+    </row>
+    <row r="1062" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1062" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1062" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1062" s="3"/>
+      <c r="D1062" s="3">
+        <v>360114611</v>
+      </c>
+      <c r="E1062" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1062" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="G1062" s="3"/>
+      <c r="H1062" s="3"/>
+      <c r="I1062" s="3"/>
+      <c r="J1062" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1062" s="3"/>
+      <c r="L1062" s="3"/>
+      <c r="M1062" s="3"/>
+    </row>
+    <row r="1063" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1063" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1063" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1063" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1063" s="3">
+        <v>360115784</v>
+      </c>
+      <c r="E1063" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1063" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="G1063" s="3"/>
+      <c r="H1063" s="3"/>
+      <c r="I1063" s="3"/>
+      <c r="J1063" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1063" s="3"/>
+      <c r="L1063" s="3"/>
+      <c r="M1063" s="3"/>
+    </row>
+    <row r="1064" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1064" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1064" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1064" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1064" s="3">
+        <v>360127814</v>
+      </c>
+      <c r="E1064" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1064" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="G1064" s="3"/>
+      <c r="H1064" s="3"/>
+      <c r="I1064" s="3"/>
+      <c r="J1064" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1064" s="3"/>
+      <c r="L1064" s="3"/>
+      <c r="M1064" s="3"/>
+    </row>
+    <row r="1065" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1065" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B1065" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1065" s="3"/>
+      <c r="D1065" s="3">
+        <v>360130958</v>
+      </c>
+      <c r="E1065" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1065" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="G1065" s="3"/>
+      <c r="H1065" s="3"/>
+      <c r="I1065" s="3"/>
+      <c r="J1065" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1065" s="3"/>
+      <c r="L1065" s="3"/>
+      <c r="M1065" s="3"/>
+    </row>
+    <row r="1066" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1066" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1066" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1066" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1066" s="3">
+        <v>360170322</v>
+      </c>
+      <c r="E1066" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1066" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G1066" s="3"/>
+      <c r="H1066" s="3"/>
+      <c r="I1066" s="3"/>
+      <c r="J1066" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1066" s="3"/>
+      <c r="L1066" s="3"/>
+      <c r="M1066" s="3"/>
+    </row>
+    <row r="1067" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1067" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1067" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1067" s="3"/>
+      <c r="D1067" s="3">
+        <v>360206232</v>
+      </c>
+      <c r="E1067" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1067" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1067" s="3"/>
+      <c r="H1067" s="3"/>
+      <c r="I1067" s="3"/>
+      <c r="J1067" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1067" s="3"/>
+      <c r="L1067" s="3"/>
+      <c r="M1067" s="3"/>
+    </row>
+    <row r="1068" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1068" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B1068" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1068" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1068" s="3">
+        <v>360254444</v>
+      </c>
+      <c r="E1068" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1068" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1068" s="3"/>
+      <c r="H1068" s="3"/>
+      <c r="I1068" s="3"/>
+      <c r="J1068" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1068" s="3"/>
+      <c r="L1068" s="3"/>
+      <c r="M1068" s="3"/>
+    </row>
+    <row r="1069" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1069" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1069" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1069" s="3">
+        <v>360347457</v>
+      </c>
+      <c r="E1069" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1069" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1069" s="3"/>
+      <c r="H1069" s="3"/>
+      <c r="I1069" s="3"/>
+      <c r="J1069" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1069" s="3"/>
+      <c r="L1069" s="3"/>
+      <c r="M1069" s="3"/>
+    </row>
+    <row r="1070" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1070" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1070" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1070" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1070" s="3">
+        <v>360353490</v>
+      </c>
+      <c r="E1070" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1070" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="G1070" s="3"/>
+      <c r="H1070" s="3"/>
+      <c r="I1070" s="3"/>
+      <c r="J1070" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1070" s="3"/>
+      <c r="L1070" s="3"/>
+      <c r="M1070" s="3"/>
+    </row>
+    <row r="1071" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1071" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1071" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1071" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1071" s="3">
+        <v>360353731</v>
+      </c>
+      <c r="E1071" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1071" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="G1071" s="3"/>
+      <c r="H1071" s="3"/>
+      <c r="I1071" s="3"/>
+      <c r="J1071" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1071" s="3"/>
+      <c r="L1071" s="3"/>
+      <c r="M1071" s="3"/>
+    </row>
+    <row r="1072" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1072" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1072" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1072" s="3">
+        <v>360469769</v>
+      </c>
+      <c r="E1072" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1072" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="G1072" s="3"/>
+      <c r="H1072" s="3">
+        <v>70</v>
+      </c>
+      <c r="I1072" s="3">
+        <v>55</v>
+      </c>
+      <c r="J1072" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1072" s="3"/>
+      <c r="L1072" s="3"/>
+      <c r="M1072" s="3"/>
+    </row>
+    <row r="1073" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1073" s="3" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1073" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1073" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1073" s="3">
+        <v>360471215</v>
+      </c>
+      <c r="E1073" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1073" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G1073" s="3"/>
+      <c r="H1073" s="3"/>
+      <c r="I1073" s="3"/>
+      <c r="J1073" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1073" s="3"/>
+      <c r="L1073" s="3"/>
+      <c r="M1073" s="3"/>
+    </row>
+    <row r="1074" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1074" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1074" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1074" s="3">
+        <v>360471608</v>
+      </c>
+      <c r="E1074" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1074" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="G1074" s="3"/>
+      <c r="H1074" s="3"/>
+      <c r="I1074" s="3"/>
+      <c r="J1074" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1074" s="3"/>
+      <c r="L1074" s="3"/>
+      <c r="M1074" s="3"/>
+    </row>
+    <row r="1075" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1075" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1075" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1075" s="3">
+        <v>360478711</v>
+      </c>
+      <c r="E1075" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1075" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G1075" s="3"/>
+      <c r="H1075" s="3"/>
+      <c r="I1075" s="3"/>
+      <c r="J1075" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1075" s="3"/>
+      <c r="L1075" s="3"/>
+      <c r="M1075" s="3"/>
+    </row>
+    <row r="1076" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1076" s="3" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1076" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1076" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1076" s="3">
+        <v>360485634</v>
+      </c>
+      <c r="E1076" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1076" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G1076" s="3"/>
+      <c r="H1076" s="3"/>
+      <c r="I1076" s="3"/>
+      <c r="J1076" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1076" s="3"/>
+      <c r="L1076" s="3"/>
+      <c r="M1076" s="3"/>
+    </row>
+    <row r="1077" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1077" s="3" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1077" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1077" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1077" s="3">
+        <v>360506448</v>
+      </c>
+      <c r="E1077" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F1077" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G1077" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1077" s="3"/>
+      <c r="I1077" s="3"/>
+      <c r="J1077" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1077" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1077" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M1077" s="3"/>
+    </row>
+    <row r="1078" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1078" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1078" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1078" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1078" s="3">
+        <v>360507578</v>
+      </c>
+      <c r="E1078" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1078" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G1078" s="3"/>
+      <c r="H1078" s="3"/>
+      <c r="I1078" s="3"/>
+      <c r="J1078" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1078" s="3"/>
+      <c r="L1078" s="3"/>
+      <c r="M1078" s="3"/>
+    </row>
+    <row r="1079" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1079" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B1079" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1079" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1079" s="3">
+        <v>360526849</v>
+      </c>
+      <c r="E1079" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1079" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G1079" s="3"/>
+      <c r="H1079" s="3"/>
+      <c r="I1079" s="3"/>
+      <c r="J1079" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1079" s="3"/>
+      <c r="L1079" s="3"/>
+      <c r="M1079" s="3"/>
+    </row>
+    <row r="1080" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1080" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1080" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1080" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1080" s="3">
+        <v>360582193</v>
+      </c>
+      <c r="E1080" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1080" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="G1080" s="3"/>
+      <c r="H1080" s="3"/>
+      <c r="I1080" s="3"/>
+      <c r="J1080" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1080" s="3"/>
+      <c r="L1080" s="3"/>
+      <c r="M1080" s="3"/>
+    </row>
+    <row r="1081" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1081" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1081" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1081" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1081" s="3">
+        <v>360595794</v>
+      </c>
+      <c r="E1081" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1081" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G1081" s="3"/>
+      <c r="H1081" s="3"/>
+      <c r="I1081" s="3"/>
+      <c r="J1081" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1081" s="3"/>
+      <c r="L1081" s="3"/>
+      <c r="M1081" s="3"/>
+    </row>
+    <row r="1082" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1082" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1082" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1082" s="3"/>
+      <c r="D1082" s="3">
+        <v>360605424</v>
+      </c>
+      <c r="E1082" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1082" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1082" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1082" s="3"/>
+      <c r="I1082" s="3"/>
+      <c r="J1082" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1082" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1082" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="M1082" s="3"/>
+    </row>
+    <row r="1083" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1083" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1083" s="3"/>
+      <c r="D1083" s="3">
+        <v>360606039</v>
+      </c>
+      <c r="E1083" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1083" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1083" s="3"/>
+      <c r="H1083" s="3"/>
+      <c r="I1083" s="3"/>
+      <c r="J1083" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1083" s="3"/>
+      <c r="L1083" s="3"/>
+      <c r="M1083" s="3"/>
+    </row>
+    <row r="1084" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1084" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1084" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1084" s="3"/>
+      <c r="D1084" s="3">
+        <v>360643182</v>
+      </c>
+      <c r="E1084" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1084" s="3" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G1084" s="3"/>
+      <c r="H1084" s="3"/>
+      <c r="I1084" s="3"/>
+      <c r="J1084" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1084" s="3"/>
+      <c r="L1084" s="3"/>
+      <c r="M1084" s="3"/>
+    </row>
+    <row r="1085" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1085" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1085" s="3"/>
+      <c r="D1085" s="3">
+        <v>360645306</v>
+      </c>
+      <c r="E1085" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1085" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G1085" s="3"/>
+      <c r="H1085" s="3"/>
+      <c r="I1085" s="3"/>
+      <c r="J1085" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1085" s="3"/>
+      <c r="L1085" s="3"/>
+      <c r="M1085" s="3"/>
+    </row>
+    <row r="1086" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1086" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B1086" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1086" s="3"/>
+      <c r="D1086" s="3">
+        <v>360646224</v>
+      </c>
+      <c r="E1086" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1086" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G1086" s="3"/>
+      <c r="H1086" s="3"/>
+      <c r="I1086" s="3"/>
+      <c r="J1086" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1086" s="3"/>
+      <c r="L1086" s="3"/>
+      <c r="M1086" s="3"/>
+    </row>
+    <row r="1087" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1087" s="3" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1087" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1087" s="3">
+        <v>360654540</v>
+      </c>
+      <c r="E1087" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1087" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="G1087" s="3"/>
+      <c r="H1087" s="3"/>
+      <c r="I1087" s="3"/>
+      <c r="J1087" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1087" s="3"/>
+      <c r="L1087" s="3"/>
+      <c r="M1087" s="3"/>
+    </row>
+    <row r="1088" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1088" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1088" s="3"/>
+      <c r="D1088" s="3">
+        <v>360669809</v>
+      </c>
+      <c r="E1088" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1088" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1088" s="3"/>
+      <c r="H1088" s="3"/>
+      <c r="I1088" s="3"/>
+      <c r="J1088" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1088" s="3"/>
+      <c r="L1088" s="3"/>
+      <c r="M1088" s="3"/>
+    </row>
+    <row r="1089" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1089" s="3" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1089" s="3"/>
+      <c r="D1089" s="3">
+        <v>360729194</v>
+      </c>
+      <c r="E1089" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1089" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G1089" s="3"/>
+      <c r="H1089" s="3"/>
+      <c r="I1089" s="3"/>
+      <c r="J1089" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1089" s="3"/>
+      <c r="L1089" s="3"/>
+      <c r="M1089" s="3"/>
+    </row>
+    <row r="1090" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1090" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1090" s="3"/>
+      <c r="D1090" s="3">
+        <v>360729394</v>
+      </c>
+      <c r="E1090" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1090" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G1090" s="3"/>
+      <c r="H1090" s="3"/>
+      <c r="I1090" s="3"/>
+      <c r="J1090" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1090" s="3"/>
+      <c r="L1090" s="3"/>
+      <c r="M1090" s="3"/>
+    </row>
+    <row r="1091" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1091" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1091" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1091" s="3"/>
+      <c r="D1091" s="3">
+        <v>360729864</v>
+      </c>
+      <c r="E1091" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1091" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1091" s="3"/>
+      <c r="H1091" s="3"/>
+      <c r="I1091" s="3"/>
+      <c r="J1091" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1091" s="3"/>
+      <c r="L1091" s="3"/>
+      <c r="M1091" s="3"/>
+    </row>
+    <row r="1092" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1092" s="3" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1092" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1092" s="3"/>
+      <c r="D1092" s="3">
+        <v>360731128</v>
+      </c>
+      <c r="E1092" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1092" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1092" s="3"/>
+      <c r="H1092" s="3"/>
+      <c r="I1092" s="3"/>
+      <c r="J1092" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1092" s="3"/>
+      <c r="L1092" s="3"/>
+      <c r="M1092" s="3"/>
+    </row>
+    <row r="1093" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1093" s="3" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B1093" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1093" s="3"/>
+      <c r="D1093" s="3">
+        <v>360731593</v>
+      </c>
+      <c r="E1093" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1093" s="3" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G1093" s="3"/>
+      <c r="H1093" s="3"/>
+      <c r="I1093" s="3"/>
+      <c r="J1093" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1093" s="3"/>
+      <c r="L1093" s="3"/>
+      <c r="M1093" s="3"/>
+    </row>
+    <row r="1094" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1094" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1094" s="3"/>
+      <c r="D1094" s="3">
+        <v>360735873</v>
+      </c>
+      <c r="E1094" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1094" s="3" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1094" s="3"/>
+      <c r="H1094" s="3"/>
+      <c r="I1094" s="3"/>
+      <c r="J1094" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1094" s="3"/>
+      <c r="L1094" s="3"/>
+      <c r="M1094" s="3"/>
+    </row>
+    <row r="1095" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1095" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B1095" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1095" s="3"/>
+      <c r="D1095" s="3">
+        <v>360736339</v>
+      </c>
+      <c r="E1095" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1095" s="3" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G1095" s="3"/>
+      <c r="H1095" s="3"/>
+      <c r="I1095" s="3"/>
+      <c r="J1095" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1095" s="3"/>
+      <c r="L1095" s="3"/>
+      <c r="M1095" s="3"/>
+    </row>
+    <row r="1096" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1096" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1096" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1096" s="3"/>
+      <c r="D1096" s="3">
+        <v>360742047</v>
+      </c>
+      <c r="E1096" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1096" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1096" s="3"/>
+      <c r="H1096" s="3"/>
+      <c r="I1096" s="3"/>
+      <c r="J1096" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1096" s="3"/>
+      <c r="L1096" s="3"/>
+      <c r="M1096" s="3"/>
+    </row>
+    <row r="1097" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1097" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B1097" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1097" s="3"/>
+      <c r="D1097" s="3">
+        <v>360742433</v>
+      </c>
+      <c r="E1097" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1097" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1097" s="3"/>
+      <c r="H1097" s="3"/>
+      <c r="I1097" s="3"/>
+      <c r="J1097" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1097" s="3"/>
+      <c r="L1097" s="3"/>
+      <c r="M1097" s="3"/>
+    </row>
+    <row r="1098" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1098" s="3" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B1098" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1098" s="3"/>
+      <c r="D1098" s="3">
+        <v>360744019</v>
+      </c>
+      <c r="E1098" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1098" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="G1098" s="3"/>
+      <c r="H1098" s="3"/>
+      <c r="I1098" s="3"/>
+      <c r="J1098" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1098" s="3"/>
+      <c r="L1098" s="3"/>
+      <c r="M1098" s="3"/>
+    </row>
+    <row r="1099" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1099" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1099" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1099" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1099" s="3">
+        <v>360765828</v>
+      </c>
+      <c r="E1099" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1099" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1099" s="3"/>
+      <c r="H1099" s="3"/>
+      <c r="I1099" s="3"/>
+      <c r="J1099" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1099" s="3"/>
+      <c r="L1099" s="3"/>
+      <c r="M1099" s="3"/>
+    </row>
+    <row r="1100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1100" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B1100" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1100" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1100" s="3">
+        <v>360768303</v>
+      </c>
+      <c r="E1100" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1100" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G1100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1100" s="3"/>
+      <c r="I1100" s="3"/>
+      <c r="J1100" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1100" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="M1100" s="3"/>
+    </row>
+    <row r="1101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1101" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1101" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1101" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1101" s="3">
+        <v>360772141</v>
+      </c>
+      <c r="E1101" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1101" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G1101" s="3"/>
+      <c r="H1101" s="3"/>
+      <c r="I1101" s="3"/>
+      <c r="J1101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1101" s="3"/>
+      <c r="L1101" s="3"/>
+      <c r="M1101" s="3"/>
+    </row>
+    <row r="1102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1102" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1102" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1102" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1102" s="3">
+        <v>360774990</v>
+      </c>
+      <c r="E1102" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1102" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G1102" s="3"/>
+      <c r="H1102" s="3"/>
+      <c r="I1102" s="3"/>
+      <c r="J1102" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1102" s="3"/>
+      <c r="L1102" s="3"/>
+      <c r="M1102" s="3"/>
+    </row>
+    <row r="1103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1103" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1103" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1103" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1103" s="3">
+        <v>360782595</v>
+      </c>
+      <c r="E1103" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1103" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1103" s="3"/>
+      <c r="H1103" s="3"/>
+      <c r="I1103" s="3"/>
+      <c r="J1103" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1103" s="3"/>
+      <c r="L1103" s="3"/>
+      <c r="M1103" s="3"/>
+    </row>
+    <row r="1104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1104" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1104" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1104" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1104" s="3">
+        <v>360790850</v>
+      </c>
+      <c r="E1104" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1104" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G1104" s="3"/>
+      <c r="H1104" s="3"/>
+      <c r="I1104" s="3"/>
+      <c r="J1104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1104" s="3"/>
+      <c r="L1104" s="3"/>
+      <c r="M1104" s="3"/>
+    </row>
+    <row r="1105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1105" s="3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B1105" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1105" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1105" s="3">
+        <v>360791588</v>
+      </c>
+      <c r="E1105" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1105" s="3" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G1105" s="3"/>
+      <c r="H1105" s="3"/>
+      <c r="I1105" s="3"/>
+      <c r="J1105" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1105" s="3"/>
+      <c r="L1105" s="3"/>
+      <c r="M1105" s="3"/>
+    </row>
+    <row r="1106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1106" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1106" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1106" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1106" s="3">
+        <v>360791793</v>
+      </c>
+      <c r="E1106" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1106" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G1106" s="3"/>
+      <c r="H1106" s="3"/>
+      <c r="I1106" s="3"/>
+      <c r="J1106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1106" s="3"/>
+      <c r="L1106" s="3"/>
+      <c r="M1106" s="3"/>
+    </row>
+    <row r="1107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1107" s="3" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1107" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1107" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1107" s="3">
+        <v>360793107</v>
+      </c>
+      <c r="E1107" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1107" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G1107" s="3"/>
+      <c r="H1107" s="3"/>
+      <c r="I1107" s="3"/>
+      <c r="J1107" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1107" s="3"/>
+      <c r="L1107" s="3"/>
+      <c r="M1107" s="3"/>
+    </row>
+    <row r="1108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1108" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1108" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1108" s="3">
+        <v>567</v>
+      </c>
+      <c r="D1108" s="3">
+        <v>360794607</v>
+      </c>
+      <c r="E1108" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1108" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1108" s="3"/>
+      <c r="H1108" s="3"/>
+      <c r="I1108" s="3"/>
+      <c r="J1108" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1108" s="3"/>
+      <c r="L1108" s="3"/>
+      <c r="M1108" s="3"/>
+    </row>
+    <row r="1109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1109" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1109" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1109" s="3">
+        <v>360929223</v>
+      </c>
+      <c r="E1109" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1109" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="G1109" s="3"/>
+      <c r="H1109" s="3"/>
+      <c r="I1109" s="3"/>
+      <c r="J1109" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1109" s="3"/>
+      <c r="L1109" s="3"/>
+      <c r="M1109" s="3"/>
+    </row>
+    <row r="1110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1110" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B1110" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1110" s="3"/>
+      <c r="D1110" s="3">
+        <v>360941993</v>
+      </c>
+      <c r="E1110" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1110" s="3" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G1110" s="3"/>
+      <c r="H1110" s="3"/>
+      <c r="I1110" s="3"/>
+      <c r="J1110" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1110" s="3"/>
+      <c r="L1110" s="3"/>
+      <c r="M1110" s="3"/>
+    </row>
+    <row r="1111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1111" s="3" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1111" s="3"/>
+      <c r="D1111" s="3">
+        <v>360948419</v>
+      </c>
+      <c r="E1111" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1111" s="3"/>
+      <c r="H1111" s="3"/>
+      <c r="I1111" s="3"/>
+      <c r="J1111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1111" s="3"/>
+      <c r="L1111" s="3"/>
+      <c r="M1111" s="3"/>
+    </row>
+    <row r="1112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1112" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1112" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1112" s="3"/>
+      <c r="D1112" s="3">
+        <v>360972736</v>
+      </c>
+      <c r="E1112" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1112" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1112" s="3"/>
+      <c r="H1112" s="3"/>
+      <c r="I1112" s="3"/>
+      <c r="J1112" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1112" s="3"/>
+      <c r="L1112" s="3"/>
+      <c r="M1112" s="3"/>
+    </row>
+    <row r="1113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1113" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B1113" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1113" s="3"/>
+      <c r="D1113" s="3">
+        <v>360985546</v>
+      </c>
+      <c r="E1113" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1113" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G1113" s="3"/>
+      <c r="H1113" s="3"/>
+      <c r="I1113" s="3"/>
+      <c r="J1113" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1113" s="3"/>
+      <c r="L1113" s="3"/>
+      <c r="M1113" s="3"/>
+    </row>
+    <row r="1114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1114" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1114" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1114" s="3"/>
+      <c r="D1114" s="3">
+        <v>360986027</v>
+      </c>
+      <c r="E1114" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1114" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1114" s="3"/>
+      <c r="H1114" s="3"/>
+      <c r="I1114" s="3"/>
+      <c r="J1114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1114" s="3"/>
+      <c r="L1114" s="3"/>
+      <c r="M1114" s="3"/>
+    </row>
+    <row r="1115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1115" s="3" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1115" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1115" s="3"/>
+      <c r="D1115" s="3">
+        <v>360986343</v>
+      </c>
+      <c r="E1115" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1115" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1115" s="3"/>
+      <c r="H1115" s="3"/>
+      <c r="I1115" s="3"/>
+      <c r="J1115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1115" s="3"/>
+      <c r="L1115" s="3"/>
+      <c r="M1115" s="3"/>
+    </row>
+    <row r="1116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1116" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1116" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1116" s="3">
+        <v>30</v>
+      </c>
+      <c r="D1116" s="3">
+        <v>360990330</v>
+      </c>
+      <c r="E1116" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1116" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1116" s="3"/>
+      <c r="H1116" s="3"/>
+      <c r="I1116" s="3"/>
+      <c r="J1116" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1116" s="3"/>
+      <c r="L1116" s="3"/>
+      <c r="M1116" s="3"/>
+    </row>
+    <row r="1117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1117" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1117" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1117" s="3">
+        <v>30</v>
+      </c>
+      <c r="D1117" s="3">
+        <v>360992967</v>
+      </c>
+      <c r="E1117" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F1117" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G1117" s="3"/>
+      <c r="H1117" s="3">
+        <v>48</v>
+      </c>
+      <c r="I1117" s="3"/>
+      <c r="J1117" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1117" s="3"/>
+      <c r="L1117" s="3"/>
+      <c r="M1117" s="3"/>
+    </row>
+    <row r="1118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1118" s="3" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1118" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1118" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1118" s="3">
+        <v>361005266</v>
+      </c>
+      <c r="E1118" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1118" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="G1118" s="3"/>
+      <c r="H1118" s="3"/>
+      <c r="I1118" s="3"/>
+      <c r="J1118" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1118" s="3"/>
+      <c r="L1118" s="3"/>
+      <c r="M1118" s="3"/>
+    </row>
+    <row r="1119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1119" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1119" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1119" s="3">
+        <v>30</v>
+      </c>
+      <c r="D1119" s="3">
+        <v>361026191</v>
+      </c>
+      <c r="E1119" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1119" s="3" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G1119" s="3"/>
+      <c r="H1119" s="3"/>
+      <c r="I1119" s="3"/>
+      <c r="J1119" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1119" s="3"/>
+      <c r="L1119" s="3"/>
+      <c r="M1119" s="3"/>
+    </row>
+    <row r="1120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1120" s="3" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1120" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1120" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1120" s="3">
+        <v>361050964</v>
+      </c>
+      <c r="E1120" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1120" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="G1120" s="3"/>
+      <c r="H1120" s="3"/>
+      <c r="I1120" s="3"/>
+      <c r="J1120" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1120" s="3"/>
+      <c r="L1120" s="3"/>
+      <c r="M1120" s="3"/>
+    </row>
+    <row r="1121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1121" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1121" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1121" s="3">
+        <v>566</v>
+      </c>
+      <c r="D1121" s="3">
+        <v>361063961</v>
+      </c>
+      <c r="E1121" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="F1121" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="G1121" s="3"/>
+      <c r="H1121" s="3"/>
+      <c r="I1121" s="3"/>
+      <c r="J1121" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1121" s="3"/>
+      <c r="L1121" s="3"/>
+      <c r="M1121" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
